--- a/evidence/pg16_race_sample_2.xlsx
+++ b/evidence/pg16_race_sample_2.xlsx
@@ -78,7 +78,7 @@
     <t>snapshot_id</t>
   </si>
   <si>
-    <t>fdf25ecd11de7174d192a27e8b94d165</t>
+    <t>668342eccc11f5a7e7ffb6a5cdce8e60</t>
   </si>
   <si>
     <t>integration_id</t>
@@ -120,13 +120,13 @@
     <t>source_snapshot_ref</t>
   </si>
   <si>
-    <t>ac55e276e85d0155bab7d044c1e00d2e</t>
+    <t>e9e9bd91834ac944619da4d4c53f1b85</t>
   </si>
   <si>
     <t>expires_at</t>
   </si>
   <si>
-    <t>2026-10-26T06:12:03Z</t>
+    <t>2026-10-26T06:23:48Z</t>
   </si>
   <si>
     <t>precision</t>

--- a/evidence/pg16_race_sample_2.xlsx
+++ b/evidence/pg16_race_sample_2.xlsx
@@ -78,7 +78,7 @@
     <t>snapshot_id</t>
   </si>
   <si>
-    <t>83669be65cc402d6da0426c6a8928bfa</t>
+    <t>bcc05e95ccd4adab6f1537416c75c4b4</t>
   </si>
   <si>
     <t>integration_id</t>
@@ -120,13 +120,13 @@
     <t>source_snapshot_ref</t>
   </si>
   <si>
-    <t>32df53c7a7bc1ca95b3107eb333a46b7</t>
+    <t>bc06cf1d6d52e4e56d97d97a75002788</t>
   </si>
   <si>
     <t>expires_at</t>
   </si>
   <si>
-    <t>2026-10-26T07:05:24Z</t>
+    <t>2026-10-26T07:29:27Z</t>
   </si>
   <si>
     <t>precision</t>
